--- a/Src/Data/Tables/MapDefine.xlsx
+++ b/Src/Data/Tables/MapDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
   <si>
     <t>类型</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>落日空间</t>
+  </si>
+  <si>
+    <t>Story</t>
   </si>
   <si>
     <t>Map03</t>
@@ -147,7 +150,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -173,11 +176,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -354,20 +352,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -393,7 +377,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -583,24 +567,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -714,182 +680,182 @@
   </borders>
   <cellStyleXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -904,16 +870,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1469,7 +1426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="2:10">
+    <row r="2" spans="1:10">
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
@@ -1530,7 +1487,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:9">
+    <row r="4" s="1" customFormat="1" spans="1:10">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1559,7 +1516,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:9">
+    <row r="5" s="1" customFormat="1" spans="1:10">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1629,7 +1586,7 @@
         <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>20</v>
@@ -1638,10 +1595,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>30</v>
@@ -1649,30 +1606,30 @@
       <c r="J7" s="7"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="8">
+      <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="2">
         <v>5</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="C8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9" t="s">
+      <c r="D8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="10"/>
+      <c r="J8" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
